--- a/Documents/PredictorScreeningTable.xlsx
+++ b/Documents/PredictorScreeningTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahhart/Library/CloudStorage/GoogleDrive-sarahjanehart13@gmail.com/My Drive/JOB/RESEARCH/Analyses/AspenHabitat/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE243E10-719D-1B40-B8FD-23B58AACFC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FC667F-7D07-8346-AF42-759B65C8088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{EC5E61FB-4842-014B-8360-6D6CF19886B2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EC5E61FB-4842-014B-8360-6D6CF19886B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Documents/PredictorScreeningTable.xlsx
+++ b/Documents/PredictorScreeningTable.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahhart/Library/CloudStorage/GoogleDrive-sarahjanehart13@gmail.com/My Drive/JOB/RESEARCH/Analyses/AspenHabitat/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FC667F-7D07-8346-AF42-759B65C8088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E53FA7-B609-5449-8957-029CB5E72B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EC5E61FB-4842-014B-8360-6D6CF19886B2}"/>
+    <workbookView xWindow="-30240" yWindow="-5760" windowWidth="14920" windowHeight="18220" activeTab="1" xr2:uid="{EC5E61FB-4842-014B-8360-6D6CF19886B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2-bak" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="119">
   <si>
     <t>Variable</t>
   </si>
@@ -250,9 +251,6 @@
 GSP/MAP</t>
   </si>
   <si>
-    <t>clay</t>
-  </si>
-  <si>
     <t>heat load index</t>
   </si>
   <si>
@@ -274,9 +272,6 @@
     <t>mean precipitation ratio: (growing season precipitation) / (mean annual precipitation)</t>
   </si>
   <si>
-    <t xml:space="preserve">Evenly distributed precipitation (intermediate PRATIO) may promote aspen by limiting seasonal  moisture stress (Rehfeltd et al. 2009) </t>
-  </si>
-  <si>
     <t xml:space="preserve">Lower relative humidity leads to greater water loss via transpiration. To limit this loss, trees may close their stomata and thereby limiting photosynthesis. </t>
   </si>
   <si>
@@ -286,9 +281,6 @@
     <t>retain - identified as important predictor by Rehfeldt et al. (2009) and (2015).</t>
   </si>
   <si>
-    <t>retain - Idenified as important predictor by Worrall et al. (2013)</t>
-  </si>
-  <si>
     <t>retain - identified as important predictor by Rehfeldt et al. (2009)</t>
   </si>
   <si>
@@ -367,28 +359,43 @@
     <t>Drop out loss</t>
   </si>
   <si>
-    <t>growing season precipitation  degree day ratio: (GSP*DD5/1000)</t>
-  </si>
-  <si>
     <t>OM</t>
   </si>
   <si>
     <t>SWC</t>
   </si>
   <si>
-    <t>Fast-growing, short-lived species such as aspen typically have high water demand (Ireland et al. 2014). Thus high ADI has been linked with lower climate suitability for aspen (Rehfeldt et al. 2009, 2015).</t>
-  </si>
-  <si>
     <t xml:space="preserve">To prevent early development of new buds that may lead to injury, aspen phenology is requires a chilling period. Insufficient chilling periods may delay budburst (Man et al. 2017). </t>
   </si>
   <si>
     <t>Greater precipitation during the growing season may alleviate summer moisture stress (Worral et al. 2013).</t>
   </si>
   <si>
-    <t>Plant productivity is higher in areas with warmer temperatures and greater precipitation during the growing season  (Rehfeldt et al. 2009).</t>
-  </si>
-  <si>
     <t>Extreme seasonal variation in temperature may present physiological challenges to aspen (Worrall et al. 2013; Rehfeldt et al. 2015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evenly distributed precipitation (intermediate PRATIO) may promote aspen by limiting seasonal moisture stress (Rehfeltd et al. 2009) </t>
+  </si>
+  <si>
+    <t>Plant productivity is higher in areas with warmer temperatures and greater precipitation during the growing season (Rehfeldt et al. 2009).</t>
+  </si>
+  <si>
+    <t>Fast-growing, short-lived species such as aspen typically have high water demand (Ireland et al. 2014). High ADI has been linked with lower climate suitability for aspen (Rehfeldt et al. 2009, 2015).</t>
+  </si>
+  <si>
+    <t>growing season precipitation degree day ratio: (GSP*DD5/1000)</t>
+  </si>
+  <si>
+    <t>clay (%)</t>
+  </si>
+  <si>
+    <t>retain - Identified as important predictor by Worrall et al. (2013)</t>
+  </si>
+  <si>
+    <t>soil organic matter content [log10(%)]</t>
+  </si>
+  <si>
+    <t>soil clay content (%)</t>
   </si>
 </sst>
 </file>
@@ -842,10 +849,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>2</v>
@@ -856,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="20">
         <v>15.6021855415503</v>
@@ -865,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34">
@@ -882,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="66" customHeight="1">
@@ -899,7 +906,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="68">
@@ -916,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="51">
@@ -924,7 +931,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C6" s="20">
         <v>2.7764791492273799</v>
@@ -933,7 +940,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="51">
@@ -950,7 +957,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="51">
@@ -967,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34">
@@ -984,7 +991,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="51">
@@ -1001,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="51">
@@ -1018,7 +1025,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34">
@@ -1035,7 +1042,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34">
@@ -1052,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="68">
@@ -1069,7 +1076,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34">
@@ -1086,7 +1093,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="33" customHeight="1">
@@ -1120,7 +1127,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34">
@@ -1137,7 +1144,7 @@
         <v>17</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34">
@@ -1154,7 +1161,7 @@
         <v>18</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="34">
@@ -1171,7 +1178,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="34">
@@ -1188,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34">
@@ -1205,7 +1212,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="34">
@@ -1222,7 +1229,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34">
@@ -1239,7 +1246,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="34">
@@ -1256,7 +1263,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="34">
@@ -1273,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="34">
@@ -1290,7 +1297,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34">
@@ -1307,7 +1314,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34">
@@ -1324,7 +1331,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34">
@@ -1341,7 +1348,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="34">
@@ -1358,7 +1365,7 @@
         <v>30</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="34">
@@ -1375,7 +1382,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="34">
@@ -1392,7 +1399,7 @@
         <v>32</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="34">
@@ -1409,7 +1416,7 @@
         <v>33</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="34">
@@ -1447,6 +1454,142 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E901A2E4-BAEB-0B47-A544-3ACE62871C4E}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="37.83203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="47" style="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="68">
+      <c r="A2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="51">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="51">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="51">
+      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="51">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="34">
+      <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34">
+      <c r="A8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34">
+      <c r="A9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="51" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="119">
+      <c r="A11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6687079A-7FBC-384D-B5D0-BCDD20DD2C65}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -1463,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="68">
@@ -1471,32 +1614,32 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="68">
       <c r="A3" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="34">
       <c r="A4" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="51">
@@ -1504,10 +1647,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="51">
@@ -1515,10 +1658,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="51">
@@ -1529,7 +1672,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="51">
@@ -1540,73 +1683,73 @@
         <v>46</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34">
       <c r="A10" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="34">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="51" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="119">
       <c r="A14" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
